--- a/admin data.xlsx
+++ b/admin data.xlsx
@@ -475,7 +475,7 @@
         <v>8100610943</v>
       </c>
       <c r="C5" t="str">
-        <v>ap2446961@gmail.com</v>
+        <v>chak.ayantika@gmail.com</v>
       </c>
       <c r="D5" t="str">
         <v>Student</v>

--- a/admin data.xlsx
+++ b/admin data.xlsx
@@ -475,7 +475,7 @@
         <v>8100610943</v>
       </c>
       <c r="C5" t="str">
-        <v>chak.ayantika@gmail.com</v>
+        <v>ap2446961@gmail.com</v>
       </c>
       <c r="D5" t="str">
         <v>Student</v>
